--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" min="1" max="1"/>
@@ -1630,6 +1630,111 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Equip_HumanToken</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>人类信物</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Icon_HumanToken</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ProtagonistEquipment</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Protagonist_ProtagonistEquipmentConfig</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>增加发现人类坟墓的概率</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Equip_ElfToken</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>精灵信物</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Icon_ElfToken</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ProtagonistEquipment</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Protagonist_ProtagonistEquipmentConfig</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>增加发现精灵坟墓的概率</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Equip_OrcToken</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>兽人信物</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Icon_OrcToken</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ProtagonistEquipment</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Protagonist_ProtagonistEquipmentConfig</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>增加发现兽人坟墓的概率</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/通用_道具汇总表_Item_ItemCatalogConfig.xlsx
@@ -2,374 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -377,309 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1032,6 +403,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1041,16 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="16.75" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="29.75" customWidth="1" min="3" max="3"/>
-    <col width="10.25" customWidth="1" min="4" max="4"/>
-    <col width="27.625" customWidth="1" min="5" max="5"/>
-    <col width="50.375" customWidth="1" min="6" max="6"/>
-  </cols>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1126,38 +490,38 @@
         </is>
       </c>
     </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ItemId</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>DisplayName</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>IconAssetId</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ItemType</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>SourceTable</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>SellPrice</t>
         </is>
@@ -1194,7 +558,7 @@
           <t>基础货币资源</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1231,7 +595,7 @@
           <t>基础制造材料</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1268,7 +632,7 @@
           <t>基础制造材料</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -1305,7 +669,7 @@
           <t>基础亡灵头部材料</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -1342,7 +706,7 @@
           <t>增加挖坟半径的主角装备</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -1379,8 +743,10 @@
           <t>装备后制造时按部位 RaceId 加权随机定种族</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1414,8 +780,10 @@
           <t>装备后，Mode2 制造的枯骨战士/战士主属性增加躯体该维之和的 15%（可叠），至彻底死亡</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1449,8 +817,10 @@
           <t>装备后，Mode2 制造时若士兵已有 Skill_01 则等级 +1（钳制到表内最大级）</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1484,8 +854,10 @@
           <t>装备后，Mode2 制造职业为 Class_BaseWarrior 的士兵时，变为 Class_Warrior</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1519,8 +891,10 @@
           <t>装备后，Mode2 制造职业为 Class_BaseArcher 的士兵时，25% 概率变为 Class_Archer</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1554,8 +928,10 @@
           <t>装备后，Mode2 制造职业为 Class_BaseMage 的士兵时，25% 概率变为 Class_Mage</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1589,8 +965,10 @@
           <t>装备后，Mode2 制造职业为 Class_BaseRogue 的士兵时，25% 概率变为 Class_Rogue</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1661,8 +1039,10 @@
           <t>增加发现人类坟墓的概率</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>20</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1696,8 +1076,10 @@
           <t>增加发现精灵坟墓的概率</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>20</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1731,8 +1113,10 @@
           <t>增加发现兽人坟墓的概率</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>20</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
     </row>
   </sheetData>
